--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981632</v>
+        <v>124981129</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495301</v>
+        <v>495341</v>
       </c>
       <c r="R2" t="n">
-        <v>6908653</v>
+        <v>6908671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981011</v>
+        <v>124981251</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495339</v>
+        <v>495301</v>
       </c>
       <c r="R3" t="n">
-        <v>6908674</v>
+        <v>6908653</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981129</v>
+        <v>124981011</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495341</v>
+        <v>495339</v>
       </c>
       <c r="R4" t="n">
-        <v>6908671</v>
+        <v>6908674</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981129</v>
+        <v>124981251</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495341</v>
+        <v>495301</v>
       </c>
       <c r="R2" t="n">
-        <v>6908671</v>
+        <v>6908653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981251</v>
+        <v>124981129</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495301</v>
+        <v>495341</v>
       </c>
       <c r="R3" t="n">
-        <v>6908653</v>
+        <v>6908671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981129</v>
+        <v>124981011</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495341</v>
+        <v>495339</v>
       </c>
       <c r="R3" t="n">
-        <v>6908671</v>
+        <v>6908674</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981011</v>
+        <v>124981129</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495339</v>
+        <v>495341</v>
       </c>
       <c r="R4" t="n">
-        <v>6908674</v>
+        <v>6908671</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981251</v>
+        <v>124981011</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495301</v>
+        <v>495339</v>
       </c>
       <c r="R2" t="n">
-        <v>6908653</v>
+        <v>6908674</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981011</v>
+        <v>124981129</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495339</v>
+        <v>495341</v>
       </c>
       <c r="R3" t="n">
-        <v>6908674</v>
+        <v>6908671</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981129</v>
+        <v>124981251</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495341</v>
+        <v>495301</v>
       </c>
       <c r="R4" t="n">
-        <v>6908671</v>
+        <v>6908653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981129</v>
+        <v>124981251</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495341</v>
+        <v>495301</v>
       </c>
       <c r="R3" t="n">
-        <v>6908671</v>
+        <v>6908653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981251</v>
+        <v>124981129</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495301</v>
+        <v>495341</v>
       </c>
       <c r="R4" t="n">
-        <v>6908653</v>
+        <v>6908671</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981011</v>
+        <v>124981632</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495339</v>
+        <v>495301</v>
       </c>
       <c r="R2" t="n">
-        <v>6908674</v>
+        <v>6908653</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981251</v>
+        <v>124981129</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495301</v>
+        <v>495341</v>
       </c>
       <c r="R3" t="n">
-        <v>6908653</v>
+        <v>6908671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981129</v>
+        <v>124981011</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495341</v>
+        <v>495339</v>
       </c>
       <c r="R4" t="n">
-        <v>6908671</v>
+        <v>6908674</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981632</v>
+        <v>124981129</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495301</v>
+        <v>495341</v>
       </c>
       <c r="R2" t="n">
-        <v>6908653</v>
+        <v>6908671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981129</v>
+        <v>124981011</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495341</v>
+        <v>495339</v>
       </c>
       <c r="R3" t="n">
-        <v>6908671</v>
+        <v>6908674</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981011</v>
+        <v>124981632</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495339</v>
+        <v>495301</v>
       </c>
       <c r="R4" t="n">
-        <v>6908674</v>
+        <v>6908653</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981632</v>
+        <v>124981251</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,7 +915,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981129</v>
+        <v>124981251</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495341</v>
+        <v>495301</v>
       </c>
       <c r="R2" t="n">
-        <v>6908671</v>
+        <v>6908653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981011</v>
+        <v>124981129</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495339</v>
+        <v>495341</v>
       </c>
       <c r="R3" t="n">
-        <v>6908674</v>
+        <v>6908671</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981251</v>
+        <v>124981011</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495301</v>
+        <v>495339</v>
       </c>
       <c r="R4" t="n">
-        <v>6908653</v>
+        <v>6908674</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981251</v>
+        <v>124981129</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495301</v>
+        <v>495341</v>
       </c>
       <c r="R2" t="n">
-        <v>6908653</v>
+        <v>6908671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981129</v>
+        <v>124981011</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495341</v>
+        <v>495339</v>
       </c>
       <c r="R3" t="n">
-        <v>6908671</v>
+        <v>6908674</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981011</v>
+        <v>124981251</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495339</v>
+        <v>495301</v>
       </c>
       <c r="R4" t="n">
-        <v>6908674</v>
+        <v>6908653</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124981129</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981011</v>
+        <v>124981632</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495339</v>
+        <v>495301</v>
       </c>
       <c r="R3" t="n">
-        <v>6908674</v>
+        <v>6908653</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124981251</v>
+        <v>124981011</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495301</v>
+        <v>495339</v>
       </c>
       <c r="R4" t="n">
-        <v>6908653</v>
+        <v>6908674</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124981129</v>
+        <v>124981632</v>
       </c>
       <c r="B2" t="n">
         <v>98269</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storkullen, Storkullen, Hjd</t>
+          <t>Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495341</v>
+        <v>495301</v>
       </c>
       <c r="R2" t="n">
-        <v>6908671</v>
+        <v>6908653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124981632</v>
+        <v>124981129</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storkullen, Hjd</t>
+          <t>Storkullen, Storkullen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495301</v>
+        <v>495341</v>
       </c>
       <c r="R3" t="n">
-        <v>6908653</v>
+        <v>6908671</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 44222-2024 artfynd.xlsx
+++ b/artfynd/A 44222-2024 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>98269</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>VU</t>
@@ -782,11 +777,6 @@
       <c r="B3" t="n">
         <v>98269</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>VU</t>
@@ -883,11 +873,6 @@
       </c>
       <c r="B4" t="n">
         <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
